--- a/光伏配储项目/电价数据/2026/如意站.xlsx
+++ b/光伏配储项目/电价数据/2026/如意站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.7605599999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.02047</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.8507899999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.59277</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.7281599999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.75193</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44267</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46034</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43239</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42707</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42537</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41335</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38814</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40518</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42868</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41717</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42097</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39547</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42486</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41557</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44794</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.13053</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.14364</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14853</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.08424</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.12264</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.46343</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.20695</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05222</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.9695</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.53392</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14906</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.22145</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23072</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23603</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21992</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.8542799999999999</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.47211</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.15652</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29057</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.46645</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.63591</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.72673</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.90573</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73066</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.59505</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.4312</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43631</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65785</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.27229</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.8798899999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.60942</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.45896</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.68928</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.84858</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.09168</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.14783</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.6543</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.26304</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8696499999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79614</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7566900000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51763</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47919</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46894</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41557</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42519</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7075900000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76505</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8696799999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9138200000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.4935</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51378</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50187</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5021100000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48441</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39901</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4665899999999999</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40516</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.85542</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.70045</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7958099999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45341</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43388</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42671</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50878</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30216</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.51366</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.78551</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9997999999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52935</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.89747</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.85275</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.50463</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.73487</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.54433</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.09805</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.03411</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47442</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.54944</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.50297</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5254800000000001</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.9054</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6231100000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.89432</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.16508</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.43243</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.17875</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.04139</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.47896</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.38128</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.53692</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.31607</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.36622</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.92279</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.25852</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9008999999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.32036</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.36141</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.2532</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.04693</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.79022</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.8102</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44869</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42788</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44334</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33457</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50708</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48612</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48664</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44746</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41384</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42721</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44257</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39516</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39466</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47149</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44362</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43742</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.46172</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.58458</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.80804</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.74817</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.68643</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.24064</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3762799999999999</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.37626</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.41021</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42379</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.56567</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.50992</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.83082</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.41141</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.60333</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.73064</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.81852</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5437000000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.15532</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6786599999999999</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.60325</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49435</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.45968</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42409</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39474</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.73638</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5179</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50573</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57089</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.59704</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.54696</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.56709</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26181</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61561</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.1179</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.49946</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.52638</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.56853</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.87658</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.91316</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.38035</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.7120299999999999</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.73963</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.60012</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.7960700000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.60923</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.83541</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56262</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.15222</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.80637</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5616599999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48575</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.61926</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45642</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34191</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5217200000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49306</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.4446</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44822</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38826</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39304</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41565</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.49615</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.65608</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.5521900000000001</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.74318</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.9874299999999999</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.67875</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.7453099999999999</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.14029</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.58638</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.24672</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.08795</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.7798099999999999</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.23411</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.81424</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.44496</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60226</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.40273</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48132</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40613</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.7563500000000001</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.7651399999999999</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.68401</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.20267</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.18135</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42534</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49344</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47357</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.52122</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.90139</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.78876</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.19683</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.84463</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.76148</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.6968300000000001</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.65562</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.57539</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.48849</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.49069</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31683</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.67477</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.7747999999999999</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.4315</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.2054</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.43776</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.40621</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.22715</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15588</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.38172</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.27403</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.19363</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.47021</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.06433</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22606</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.41994</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21349</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06542000000000001</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.10653</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.01385</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00399</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.17735</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27122</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29763</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.9007200000000001</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.88658</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.89232</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>1.38914</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>1.39052</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48297</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34276</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.57487</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.39622</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.14426</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.37434</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.27939</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.25318</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.27858</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.30598</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29026</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10283</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04361</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04475</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01571</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21708</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05468</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20772</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.08148000000000001</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07122000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06945999999999999</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>1.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>1.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>1.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>1.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33064</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31162</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42737</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45502</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7851900000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8628899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87985</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.31887</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33086</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53079</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.81062</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49316</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.3999</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44952</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.40808</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42507</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38634</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44901</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5534</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4069700000000001</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58204</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.70255</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87571</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46588</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.54653</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43058</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8051900000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.5587000000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8512799999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>1.15909</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.6154500000000001</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6215599999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59163</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1.16942</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.28246</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.29862</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.41792</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34632</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91303</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44008</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40373</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.43209</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.38646</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.45491</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28747</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.19379</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27301</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1974</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25315</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.39369</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.43369</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.49003</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.43711</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.44015</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.43575</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.40644</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.43795</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.39657</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.52203</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8610800000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.43861</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.79323</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.90944</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.63503</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59534</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.49168</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.43771</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.48754</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.42821</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40295</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40273</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.40066</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.45565</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40302</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42337</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.41169</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41459</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>1.3886</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>1.38879</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>1.37455</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>1.48481</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.50088</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28591</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.53043</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.49406</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.44625</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.93035</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.54826</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.71693</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.88405</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.35549</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.5978</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.44785</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.51403</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15472</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27321</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27522</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01071</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.33416</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.30112</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.54936</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.5630499999999999</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.78071</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.28141</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.7097100000000001</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.87417</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.88691</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>1.30328</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>1.31009</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>1.31775</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.31663</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.31016</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>1.3261</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.32791</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.53451</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>1.38113</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.34257</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.35108</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>1.3315</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.31893</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5414500000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43176</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7836000000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.43294</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43452</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44065</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3068</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.29823</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.28849</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.28037</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.27532</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.23068</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.28323</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.23488</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.23268</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.26848</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26029</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23021</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.26089</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.40253</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.25499</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.26864</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.27672</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.48015</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.4402</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.37601</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.40345</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4041</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.40844</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43681</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38135</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38307</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33214</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.48303</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.42978</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.39531</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.41394</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29858</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.98198</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.7070299999999999</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25416</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27943</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23931</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.46924</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.47021</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.5177200000000001</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.49021</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.39781</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.6951900000000001</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.64986</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.39022</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.7242999999999999</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.89013</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.65338</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.92525</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.09517</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.40515</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44353</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.34672</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.45344</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.4663</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.42596</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.7973</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.9180199999999999</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.9031</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.43628</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.81865</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.48116</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.16164</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.90063</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.8845</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.13028</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.85539</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.32085</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.19057</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.2252</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.80623</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.28254</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.43219</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.47378</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.59711</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.35607</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.27878</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.4307</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.69453</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.55262</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.4347</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.55694</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.23385</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.50657</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.88229</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.71092</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.66901</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.19588</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.67569</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.64355</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.73138</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.6607799999999999</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.65466</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.15945</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.78095</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.46379</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.7601599999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.74207</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.0173</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.68992</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.63839</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.59633</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.50888</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5022099999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.23898</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.7057899999999999</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30495</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.5454600000000001</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41237</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.29947</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.9662500000000001</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.45367</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27564</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.75988</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.05966</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.3386</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.9889199999999999</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.49158</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.75459</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.74949</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34195</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.26355</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29892</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.69986</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.20799</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.5237999999999999</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.41413</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.4055</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.47765</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56109</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.42237</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.46924</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.5767599999999999</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6496799999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.42379</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.58516</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.5719299999999999</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.82594</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.6738200000000001</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33231</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.17995</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.44151</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.73576</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.5062</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.75517</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.43288</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.5879500000000001</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.82284</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28813</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.6096699999999999</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.40579</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.64839</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.51463</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.77106</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.67336</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.10788</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.63691</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.61403</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.8288099999999999</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.6429600000000001</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.81702</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.15305</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.14911</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.18397</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.94489</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.90271</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.22458</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.78859</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.03171</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.79889</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.59136</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.76508</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.78944</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.70068</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.20433</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.13214</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.67801</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.34858</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.44845</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.51812</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46702</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6030800000000001</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.38949</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.40732</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.41016</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.4926</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.45153</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.44902</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41368</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.5701799999999999</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.15041</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.82821</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.19768</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.23432</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.56269</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.31389</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42677</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.56376</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.56647</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.59023</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.73933</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.5782999999999999</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.48186</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.51323</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.5043299999999999</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.58374</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.83274</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.85922</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.16865</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.5571</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.56432</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.54849</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.54676</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.8814500000000001</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.38899</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.40798</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.45092</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.41438</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.46351</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.4636</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.4948</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.60537</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.70689</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.79492</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.57109</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.6918200000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.76934</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.8063899999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7111499999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7640399999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61672</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66488</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.83965</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.6390399999999999</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.44092</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.4377</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.43093</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.49579</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40102</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.41126</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42105</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42681</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.41278</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40846</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.40802</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.45173</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.28036</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39442</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.37893</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.77142</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.56162</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.5331</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.52934</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.5505800000000001</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.5396599999999999</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.74963</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.55162</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.62767</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.58821</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.6371100000000001</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.24527</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.16369</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.22463</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.55911</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.44347</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42292</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41969</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.32487</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.45127</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.87158</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.7749400000000001</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.28172</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.26616</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.26374</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.26372</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.25205</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.28691</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.29045</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.24481</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.24391</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.23756</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.28334</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.27505</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.23253</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.18055</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28172</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24908</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27011</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26508</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26102</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.08929999999999999</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.26499</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25883</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03246</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28216</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.20069</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.28589</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.25287</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.27134</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25746</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24183</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27627</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2849100000000001</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27326</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.45468</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30133</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.77218</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.44109</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.40723</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.30037</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.31815</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.6080800000000001</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.25958</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.28809</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.28372</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.22717</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.28636</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.23884</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.22591</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.2293</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.22928</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.22619</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.22619</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.22805</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.27781</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.22223</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.22619</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.22605</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.22585</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23312</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15507</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26548</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.2018</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01162</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00027</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14523</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02121</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01544</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04285</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04074000000000001</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04858</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04824000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02923</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.2742</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03836999999999999</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01936</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03619</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20113</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26458</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28806</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27901</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.23045</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.4138</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.3274</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.71026</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.6117400000000001</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.40318</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.41472</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.28608</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.24494</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.24315</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22447</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.25786</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24934</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.27732</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24361</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.27034</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28171</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43519</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.24942</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.63219</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.80592</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8752799999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85017</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.13063</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.21298</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.26788</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.04244</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.26165</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.27412</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.02589</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.009980000000000001</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06719</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28779</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30154</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25893</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47123</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.40195</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.47652</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.78995</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.75149</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.77579</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.33587</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.00609</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.7524999999999999</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.8356399999999999</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.77195</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83917</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83736</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8416699999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9389400000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.7300099999999999</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.76791</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7335700000000001</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36035</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.45854</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.59399</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.6096699999999999</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.55671</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49226</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.45242</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.46405</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.26457</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.45321</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.46216</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41713</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.44244</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.42418</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.39537</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.40609</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.41177</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.41621</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.47481</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46817</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.73151</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.44587</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.60563</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.47452</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.42165</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.42345</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.46009</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33425</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.41837</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40365</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.5355700000000001</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.74971</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.5346599999999999</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.54737</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.40495</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39742</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.45217</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.42919</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.44593</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.44687</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.44555</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.42956</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.95237</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.6070800000000001</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.50178</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.02573</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.80535</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.06815</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.75714</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.1044</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.95162</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.72224</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.5669</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.44825</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.44623</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.61246</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.70108</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.8166100000000001</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.46239</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23237</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.34962</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.44977</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.37827</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37336</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.8857200000000001</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.54696</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.40595</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.56952</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.43457</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.38417</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.4819</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.44725</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37232</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41674</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51223</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.79213</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.6967100000000001</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.68104</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.67837</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.03181</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.6180399999999999</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47219</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.18481</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.9305800000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.0483</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.96935</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.7830199999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.64164</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.64254</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.41866</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35402</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.21028</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37392</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.42617</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.25933</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.90604</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.49188</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.74275</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.9341799999999999</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.52755</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.27068</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.97113</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.49622</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.46576</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>1.00388</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.58714</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.48691</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.90332</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.31098</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.4919</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.89442</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>1.03649</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.89855</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.5126900000000001</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.42441</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.4067</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.4357799999999999</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.91214</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.79189</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.41731</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.55733</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.00652</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.57416</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.32784</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.6015199999999999</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.92328</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.45579</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.63474</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.36867</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.58301</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.62376</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.58689</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.86003</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39663</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.42712</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40221</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.47301</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36045</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.13998</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.79335</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.55632</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.59762</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.86502</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36433</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.43773</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.7104400000000001</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.44654</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.6209199999999999</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.44549</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.89211</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.6771200000000001</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.44445</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42575</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.43757</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.45965</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.5783200000000001</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.52623</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.49653</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.43333</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.9480700000000001</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.15492</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.8831100000000001</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.51159</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.6303099999999999</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.7348300000000001</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.6759400000000001</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35705</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37484</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37319</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17551</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29447</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14519</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19782</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14184</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.0445</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12187</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22679</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26733</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.15184</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14405</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.1968</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22594</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26137</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15253</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15213</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19627</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14201</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27884</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.40918</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.29628</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.40452</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.41343</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.88024</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.64206</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.48574</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.15498</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.5099</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.44503</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38178</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.44307</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49255</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.49682</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44593</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38385</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38184</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38301</v>
       </c>
     </row>
   </sheetData>
